--- a/Tutor_Emergencies.xlsx
+++ b/Tutor_Emergencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb0a5f6c6df775a3/BRNC/Tutor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0230FCB2-81D2-4E50-847A-40AFF8EEFDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{0230FCB2-81D2-4E50-847A-40AFF8EEFDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{530A701A-959D-4FCF-A6F2-B7B4EFC89E0B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{52106DAB-FC63-4434-9466-B4BEC8133BB0}"/>
+    <workbookView xWindow="22932" yWindow="672" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{52106DAB-FC63-4434-9466-B4BEC8133BB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Engine_Fire" sheetId="1" r:id="rId1"/>
@@ -41,26 +41,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
-  <si>
-    <t>Indication</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
   <si>
     <t>Actions</t>
   </si>
   <si>
-    <t>Result</t>
-  </si>
-  <si>
     <t>Conditional</t>
   </si>
   <si>
     <t>Order</t>
   </si>
   <si>
-    <t>Engine Fire</t>
-  </si>
-  <si>
     <t>RPM As required</t>
   </si>
   <si>
@@ -80,12 +71,6 @@
   </si>
   <si>
     <t>Fuel cock OFF</t>
-  </si>
-  <si>
-    <t>Engine Failure (Mechanical)</t>
-  </si>
-  <si>
-    <t>Engine Failure (Non-Mechanical)</t>
   </si>
   <si>
     <t>ALTERN. AIR Hot</t>
@@ -481,13 +466,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2515C41-371A-498F-AF80-B210648B872C}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,69 +482,60 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="b">
+      <c r="C8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -570,13 +546,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48055FD3-68A9-4D93-9B55-063C3F3B311A}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -586,69 +562,60 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="b">
+      <c r="C8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -659,13 +626,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB39285-A695-4F42-97DB-11AA66D8EFE4}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -675,75 +642,66 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Tutor_Emergencies.xlsx
+++ b/Tutor_Emergencies.xlsx
@@ -5,17 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb0a5f6c6df775a3/BRNC/Tutor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb0a5f6c6df775a3/BRNC/Tutor/Emergencies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{0230FCB2-81D2-4E50-847A-40AFF8EEFDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{530A701A-959D-4FCF-A6F2-B7B4EFC89E0B}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{0230FCB2-81D2-4E50-847A-40AFF8EEFDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AADB5279-6956-43A5-8C7F-194D4B1A3472}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="672" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{52106DAB-FC63-4434-9466-B4BEC8133BB0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{52106DAB-FC63-4434-9466-B4BEC8133BB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Engine_Fire" sheetId="1" r:id="rId1"/>
     <sheet name="Engine_Failure_(Mechanical)" sheetId="2" r:id="rId2"/>
     <sheet name="Engine_Failure_(Non_Mechanical)" sheetId="4" r:id="rId3"/>
+    <sheet name="ROUGH_RUNNING" sheetId="6" r:id="rId4"/>
+    <sheet name="STARTER_WARNING_IN_FLIGHT" sheetId="7" r:id="rId5"/>
+    <sheet name="FIRE_ON_GROUND" sheetId="8" r:id="rId6"/>
+    <sheet name="COCKPIT_FIRE_(ELECTRICAL)" sheetId="9" r:id="rId7"/>
+    <sheet name="FUMES_IN_COCKPIT_(CO_ALARM)" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="32">
   <si>
     <t>Actions</t>
   </si>
@@ -52,9 +57,6 @@
     <t>Order</t>
   </si>
   <si>
-    <t>RPM As required</t>
-  </si>
-  <si>
     <t>Mixture lever Ungate</t>
   </si>
   <si>
@@ -70,15 +72,6 @@
     <t>GEN switch OFF</t>
   </si>
   <si>
-    <t>Fuel cock OFF</t>
-  </si>
-  <si>
-    <t>ALTERN. AIR Hot</t>
-  </si>
-  <si>
-    <t>THROTTLE IDLE</t>
-  </si>
-  <si>
     <t>Mixture lever RICH</t>
   </si>
   <si>
@@ -88,13 +81,67 @@
     <t>Fuel Cock ON</t>
   </si>
   <si>
-    <t>Aux FUEL PUMP On</t>
-  </si>
-  <si>
     <t>FUEL QTY Check Contents</t>
   </si>
   <si>
     <t>Fuel selector BOTH</t>
+  </si>
+  <si>
+    <t>RPM Lever As required</t>
+  </si>
+  <si>
+    <t>ALTERN. AIR HOT</t>
+  </si>
+  <si>
+    <t>THROTTLE to IDLE</t>
+  </si>
+  <si>
+    <t>Aux FUEL PUMP ON</t>
+  </si>
+  <si>
+    <t>Positive G Applied</t>
+  </si>
+  <si>
+    <t>LAND ASAP</t>
+  </si>
+  <si>
+    <t>START CTRL CB Pull</t>
+  </si>
+  <si>
+    <t>MAIN BUS CB PULL</t>
+  </si>
+  <si>
+    <t>BAT switch OFF</t>
+  </si>
+  <si>
+    <t>If STARTER caption remains lit:</t>
+  </si>
+  <si>
+    <t>Fuel Cock OFF</t>
+  </si>
+  <si>
+    <t>Radio Distress Call (if circumstances permit)</t>
+  </si>
+  <si>
+    <t>ELT ON</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Operate if required</t>
+  </si>
+  <si>
+    <t>Cabin conditioning Cold, screen</t>
+  </si>
+  <si>
+    <t>Air vents Open</t>
+  </si>
+  <si>
+    <t>Speed Below 80 kts if possible</t>
+  </si>
+  <si>
+    <t>Canopy Set ventilation position</t>
+  </si>
+  <si>
+    <t>CO DETECTOR CHECK</t>
   </si>
 </sst>
 </file>
@@ -147,6 +194,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,7 +536,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -493,7 +544,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -501,7 +552,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -509,7 +560,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -517,7 +568,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -525,7 +576,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -533,7 +584,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
@@ -565,7 +616,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -573,7 +624,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -581,7 +632,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -589,7 +640,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -597,7 +648,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -605,7 +656,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -613,7 +664,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
@@ -645,7 +696,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -653,7 +704,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -661,7 +712,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -669,7 +720,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -677,7 +728,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -685,7 +736,95 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C95086F6-C483-4242-B947-FDF2F2F53D2A}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -701,7 +840,281 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{804DD45B-611F-4698-8937-8889EA317647}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{145A916E-B2A5-4BF2-AE6D-08FC88C477B1}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282D0B11-626D-4D67-A271-FE7B65F3196A}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719A3407-2A8E-4639-8E8A-2BC98D7A4150}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Tutor_Emergencies.xlsx
+++ b/Tutor_Emergencies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb0a5f6c6df775a3/BRNC/Tutor/Emergencies/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/EB0A5F6C6DF775A3/BRNC/Tutor/Emergencies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{0230FCB2-81D2-4E50-847A-40AFF8EEFDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AADB5279-6956-43A5-8C7F-194D4B1A3472}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{0230FCB2-81D2-4E50-847A-40AFF8EEFDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED4662DD-8FCE-4ECC-AB16-F5EAFD3A706B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{52106DAB-FC63-4434-9466-B4BEC8133BB0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="9" xr2:uid="{52106DAB-FC63-4434-9466-B4BEC8133BB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Engine_Fire" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="FIRE_ON_GROUND" sheetId="8" r:id="rId6"/>
     <sheet name="COCKPIT_FIRE_(ELECTRICAL)" sheetId="9" r:id="rId7"/>
     <sheet name="FUMES_IN_COCKPIT_(CO_ALARM)" sheetId="10" r:id="rId8"/>
+    <sheet name="LOW_OIL_PRESSURE_WARNING" sheetId="11" r:id="rId9"/>
+    <sheet name="FUEL_WARNING" sheetId="13" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="34">
   <si>
     <t>Actions</t>
   </si>
@@ -142,6 +144,12 @@
   </si>
   <si>
     <t>CO DETECTOR CHECK</t>
+  </si>
+  <si>
+    <t>THROTTLE Set approx 20'' MP</t>
+  </si>
+  <si>
+    <t>IAS Minimise changes</t>
   </si>
 </sst>
 </file>
@@ -194,10 +202,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -518,12 +522,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2515C41-371A-498F-AF80-B210648B872C}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -534,7 +538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -542,7 +546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -550,7 +554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -558,7 +562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -566,7 +570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -574,7 +578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -582,7 +586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -595,15 +599,64 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C76A7ED9-B9B3-4A71-AA4A-BF83BFCF76D9}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48055FD3-68A9-4D93-9B55-063C3F3B311A}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -614,7 +667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -622,7 +675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -630,7 +683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -638,7 +691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -646,7 +699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -654,7 +707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -662,7 +715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -678,12 +731,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB39285-A695-4F42-97DB-11AA66D8EFE4}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -694,7 +747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -702,7 +755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -710,7 +763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -718,7 +771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -726,7 +779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -734,7 +787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -742,7 +795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -750,7 +803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -766,12 +819,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C95086F6-C483-4242-B947-FDF2F2F53D2A}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -782,7 +835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -790,7 +843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -798,7 +851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -806,7 +859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -814,7 +867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -822,7 +875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -830,7 +883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -838,7 +891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -846,7 +899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -854,7 +907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -870,13 +923,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{804DD45B-611F-4698-8937-8889EA317647}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="27.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -887,7 +940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -898,7 +951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -906,7 +959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -922,13 +975,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{145A916E-B2A5-4BF2-AE6D-08FC88C477B1}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -939,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -947,7 +1000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -955,7 +1008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -963,7 +1016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -971,7 +1024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -979,7 +1032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -990,7 +1043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1006,13 +1059,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282D0B11-626D-4D67-A271-FE7B65F3196A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1023,7 +1076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1031,7 +1084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1039,7 +1092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1047,7 +1100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -1063,13 +1116,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719A3407-2A8E-4639-8E8A-2BC98D7A4150}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="40.42578125" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1080,7 +1133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -1088,7 +1141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1096,7 +1149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1104,7 +1157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1112,9 +1165,53 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>31</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABEE9B6-16DD-4802-A342-364F8FF1D39D}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
